--- a/data/trans_camb/P6904-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P6904-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 13,57</t>
+          <t>-29,26; 13,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-43,49; -3,29</t>
+          <t>-45,4; -5,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,01; 16,11</t>
+          <t>-35,12; 14,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 39,26</t>
+          <t>-14,39; 41,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 38,65</t>
+          <t>-6,96; 42,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 53,0</t>
+          <t>-0,02; 54,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 18,38</t>
+          <t>-16,09; 17,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 7,25</t>
+          <t>-23,82; 7,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 24,37</t>
+          <t>-13,78; 24,51</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,04; 23,78</t>
+          <t>-40,15; 23,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-59,38; -6,76</t>
+          <t>-61,48; -9,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,03; 27,21</t>
+          <t>-49,09; 26,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 113,17</t>
+          <t>-21,87; 111,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 102,84</t>
+          <t>-10,72; 119,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 152,91</t>
+          <t>2,57; 154,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 34,69</t>
+          <t>-23,52; 34,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 13,57</t>
+          <t>-35,27; 13,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 47,46</t>
+          <t>-19,73; 46,44</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 34,42</t>
+          <t>-4,28; 32,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,18; 39,28</t>
+          <t>8,45; 39,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 29,48</t>
+          <t>-14,76; 28,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-43,47; 5,16</t>
+          <t>-42,88; 7,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 43,0</t>
+          <t>-1,93; 41,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,83; 15,95</t>
+          <t>-28,05; 16,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 17,54</t>
+          <t>-11,91; 16,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,09; 36,03</t>
+          <t>11,24; 36,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 17,24</t>
+          <t>-12,43; 18,12</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 88,05</t>
+          <t>-6,27; 84,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,13; 96,92</t>
+          <t>14,42; 99,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,68; 71,05</t>
+          <t>-26,98; 66,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,95; 11,29</t>
+          <t>-63,59; 17,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 98,08</t>
+          <t>-1,84; 96,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,65; 37,24</t>
+          <t>-39,3; 37,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 39,38</t>
+          <t>-20,17; 36,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,59; 81,69</t>
+          <t>19,35; 83,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 38,52</t>
+          <t>-20,69; 39,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,27; 31,91</t>
+          <t>-17,85; 30,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,94; 49,05</t>
+          <t>5,52; 49,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 18,66</t>
+          <t>-25,05; 16,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 36,92</t>
+          <t>-25,54; 38,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 55,54</t>
+          <t>-16,11; 52,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 38,85</t>
+          <t>-9,95; 37,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 25,22</t>
+          <t>-13,52; 27,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,11; 44,77</t>
+          <t>5,45; 43,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 18,11</t>
+          <t>-12,63; 20,25</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,08; 77,49</t>
+          <t>-29,38; 72,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,16; 125,97</t>
+          <t>7,1; 118,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-37,4; 47,29</t>
+          <t>-39,48; 41,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,4; 143,48</t>
+          <t>-48,44; 137,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 232,63</t>
+          <t>-27,58; 215,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 183,12</t>
+          <t>-17,48; 154,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,02; 66,98</t>
+          <t>-25,04; 74,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,7; 124,45</t>
+          <t>12,71; 119,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 45,92</t>
+          <t>-20,47; 52,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 28,21</t>
+          <t>-11,55; 30,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,49; 47,66</t>
+          <t>4,29; 46,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,65; 54,12</t>
+          <t>11,34; 51,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 36,48</t>
+          <t>-17,38; 37,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 51,11</t>
+          <t>-4,34; 47,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,05; 72,04</t>
+          <t>25,15; 71,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 24,81</t>
+          <t>-5,0; 27,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,76; 41,86</t>
+          <t>9,33; 43,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,24; 60,85</t>
+          <t>28,09; 56,42</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 85,23</t>
+          <t>-22,97; 93,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,66; 150,64</t>
+          <t>8,7; 146,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,39; 172,24</t>
+          <t>23,19; 171,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 154,09</t>
+          <t>-32,12; 155,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 217,91</t>
+          <t>-7,99; 208,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,36; 363,65</t>
+          <t>37,87; 327,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 74,9</t>
+          <t>-12,23; 80,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,5; 129,15</t>
+          <t>17,99; 129,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>56,22; 192,32</t>
+          <t>53,49; 175,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22,5; 72,69</t>
+          <t>17,98; 70,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 49,3</t>
+          <t>-19,02; 49,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 33,52</t>
+          <t>-20,63; 35,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 83,19</t>
+          <t>0,73; 83,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,57; 100,0</t>
+          <t>8,23; 100,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 55,58</t>
+          <t>-7,86; 58,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,56; 65,68</t>
+          <t>18,12; 64,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 57,46</t>
+          <t>-1,07; 55,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 33,37</t>
+          <t>-11,49; 32,32</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>39,91; 324,8</t>
+          <t>30,11; 311,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 190,92</t>
+          <t>-33,09; 183,58</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,37; 149,05</t>
+          <t>-39,76; 146,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,7; 321,87</t>
+          <t>37,21; 350,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,4; 263,23</t>
+          <t>-1,52; 260,24</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 177,0</t>
+          <t>-22,09; 158,33</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 35,73</t>
+          <t>-4,94; 37,74</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-28,54; 20,62</t>
+          <t>-31,25; 20,71</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 41,06</t>
+          <t>-1,37; 43,28</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-50,48; 16,33</t>
+          <t>-50,27; 18,84</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 73,55</t>
+          <t>5,97; 73,01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 44,03</t>
+          <t>-16,76; 42,99</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 25,86</t>
+          <t>-10,17; 27,28</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 29,5</t>
+          <t>-14,97; 29,66</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,47; 36,25</t>
+          <t>2,63; 36,25</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 133,29</t>
+          <t>-9,93; 137,14</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-58,78; 67,44</t>
+          <t>-63,68; 64,99</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 153,89</t>
+          <t>-2,66; 155,39</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-85,34; 92,27</t>
+          <t>-84,92; 108,5</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5,91; 411,42</t>
+          <t>13,63; 386,15</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 234,16</t>
+          <t>-26,42; 205,27</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 83,41</t>
+          <t>-21,9; 91,18</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-31,26; 94,82</t>
+          <t>-33,01; 93,71</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2,05; 123,14</t>
+          <t>5,18; 121,28</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 8,81</t>
+          <t>-25,13; 11,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,05; 32,38</t>
+          <t>0,39; 32,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 23,43</t>
+          <t>-9,24; 23,41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 26,31</t>
+          <t>-15,85; 25,34</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 26,8</t>
+          <t>-13,62; 28,27</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 31,56</t>
+          <t>-4,95; 31,05</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 13,41</t>
+          <t>-15,35; 11,99</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,16; 26,11</t>
+          <t>1,04; 24,53</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,09; 23,01</t>
+          <t>-1,13; 23,48</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-45,39; 19,98</t>
+          <t>-45,92; 27,7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3,17; 78,84</t>
+          <t>0,69; 80,61</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 56,03</t>
+          <t>-15,95; 57,82</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 63,46</t>
+          <t>-25,9; 63,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 69,64</t>
+          <t>-21,77; 72,57</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 78,94</t>
+          <t>-6,69; 83,14</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-24,96; 31,07</t>
+          <t>-27,57; 26,67</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2,21; 64,19</t>
+          <t>1,86; 57,63</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,35; 53,78</t>
+          <t>-1,41; 56,21</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-38,53; -4,88</t>
+          <t>-37,17; -3,83</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-43,12; -7,56</t>
+          <t>-44,81; -6,75</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 27,49</t>
+          <t>-3,49; 26,48</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-30,76; 15,12</t>
+          <t>-29,16; 14,73</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-35,09; 15,16</t>
+          <t>-35,35; 15,79</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 13,28</t>
+          <t>-29,73; 10,71</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-28,44; -2,12</t>
+          <t>-29,92; -2,34</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-34,43; -4,72</t>
+          <t>-34,63; -3,71</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 13,19</t>
+          <t>-9,65; 12,57</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-57,35; -6,76</t>
+          <t>-56,53; -6,15</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-63,83; -11,72</t>
+          <t>-66,47; -10,87</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 50,39</t>
+          <t>-3,81; 48,44</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-43,38; 29,23</t>
+          <t>-42,21; 26,4</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-51,6; 25,41</t>
+          <t>-52,88; 28,24</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-40,15; 25,3</t>
+          <t>-41,32; 21,15</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-42,85; -3,54</t>
+          <t>-44,8; -3,88</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-52,47; -7,95</t>
+          <t>-52,45; -6,42</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 22,85</t>
+          <t>-14,58; 21,6</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 10,3</t>
+          <t>-4,68; 10,44</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 13,99</t>
+          <t>0,07; 14,69</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,56; 16,46</t>
+          <t>1,59; 16,34</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 9,21</t>
+          <t>-10,06; 8,83</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,56; 24,63</t>
+          <t>6,34; 24,1</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,84; 25,38</t>
+          <t>4,7; 25,75</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 7,42</t>
+          <t>-4,55; 7,75</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>4,49; 16,13</t>
+          <t>4,89; 16,14</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5,64; 17,91</t>
+          <t>5,54; 17,43</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 20,97</t>
+          <t>-8,45; 21,19</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 27,9</t>
+          <t>0,2; 29,9</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2,88; 33,9</t>
+          <t>2,79; 33,37</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 19,86</t>
+          <t>-17,56; 18,63</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>11,58; 54,02</t>
+          <t>10,71; 51,4</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>8,3; 54,0</t>
+          <t>7,51; 52,87</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 15,19</t>
+          <t>-8,52; 16,0</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>8,28; 32,51</t>
+          <t>9,09; 32,63</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>10,6; 36,72</t>
+          <t>10,16; 35,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6904-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P6904-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-8,69</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,85</t>
+          <t>26,53</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>10,54</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 13,54</t>
+          <t>-31,46; 13,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-45,4; -5,73</t>
+          <t>-46,36; -5,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-35,12; 14,93</t>
+          <t>-22,74; 21,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 41,89</t>
+          <t>-14,99; 39,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 42,18</t>
+          <t>-6,58; 39,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 54,53</t>
+          <t>0,19; 50,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 17,83</t>
+          <t>-17,33; 18,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 7,0</t>
+          <t>-25,18; 7,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 24,51</t>
+          <t>-7,68; 28,77</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-13,09%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,15; 23,0</t>
+          <t>-41,95; 22,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-61,48; -9,65</t>
+          <t>-63,37; -10,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,09; 26,02</t>
+          <t>-30,56; 37,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 111,91</t>
+          <t>-22,86; 102,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 119,76</t>
+          <t>-10,85; 113,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 154,85</t>
+          <t>1,16; 135,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 34,75</t>
+          <t>-25,44; 37,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 13,19</t>
+          <t>-35,67; 15,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 46,44</t>
+          <t>-11,38; 54,59</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,85</t>
+          <t>9,05</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-6,02</t>
+          <t>-4,89</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>3,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 32,94</t>
+          <t>-4,29; 33,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,45; 39,19</t>
+          <t>8,26; 39,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 28,27</t>
+          <t>-15,83; 28,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-42,88; 7,27</t>
+          <t>-42,73; 7,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 41,89</t>
+          <t>-0,53; 41,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 16,12</t>
+          <t>-26,12; 17,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 16,43</t>
+          <t>-12,41; 15,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,24; 36,22</t>
+          <t>9,94; 36,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 18,12</t>
+          <t>-10,63; 17,32</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-10,31%</t>
+          <t>-8,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 84,44</t>
+          <t>-6,9; 86,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,42; 99,74</t>
+          <t>14,29; 103,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,98; 66,62</t>
+          <t>-25,61; 69,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,59; 17,68</t>
+          <t>-62,89; 16,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 96,55</t>
+          <t>-1,22; 100,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,3; 37,37</t>
+          <t>-36,69; 40,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 36,61</t>
+          <t>-21,64; 33,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,35; 83,46</t>
+          <t>16,74; 81,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 39,33</t>
+          <t>-18,27; 38,56</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,83</t>
+          <t>-2,12</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,24</t>
+          <t>14,77</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>4,57</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 30,39</t>
+          <t>-16,48; 32,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 49,1</t>
+          <t>4,91; 48,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 16,94</t>
+          <t>-24,9; 19,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 38,2</t>
+          <t>-26,59; 34,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 52,07</t>
+          <t>-13,18; 54,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 37,06</t>
+          <t>-10,47; 37,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 27,87</t>
+          <t>-13,32; 26,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 43,78</t>
+          <t>3,93; 43,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 20,25</t>
+          <t>-11,55; 20,76</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-5,24%</t>
+          <t>-3,92%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,38; 72,06</t>
+          <t>-25,45; 79,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,1; 118,25</t>
+          <t>10,79; 127,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-39,48; 41,54</t>
+          <t>-36,82; 48,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-48,44; 137,21</t>
+          <t>-53,8; 138,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,58; 215,9</t>
+          <t>-22,84; 245,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 154,41</t>
+          <t>-16,38; 170,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 74,12</t>
+          <t>-22,96; 69,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,71; 119,09</t>
+          <t>9,0; 113,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 52,34</t>
+          <t>-19,02; 53,58</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34,76</t>
+          <t>32,14</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,33</t>
+          <t>38,86</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>42,27</t>
+          <t>35,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 30,57</t>
+          <t>-11,8; 30,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,29; 46,12</t>
+          <t>4,07; 48,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,34; 51,69</t>
+          <t>10,42; 51,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 37,15</t>
+          <t>-17,11; 38,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 47,53</t>
+          <t>-3,92; 50,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,15; 71,55</t>
+          <t>13,05; 61,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 27,66</t>
+          <t>-6,83; 25,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,33; 43,38</t>
+          <t>9,34; 42,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28,09; 56,42</t>
+          <t>21,94; 48,95</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>112,58%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>101,76%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,97; 93,19</t>
+          <t>-23,17; 99,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,7; 146,98</t>
+          <t>8,39; 162,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,19; 171,91</t>
+          <t>20,05; 167,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-32,12; 155,14</t>
+          <t>-31,45; 152,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 208,33</t>
+          <t>-7,57; 219,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,87; 327,02</t>
+          <t>22,94; 276,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 80,84</t>
+          <t>-14,79; 73,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,99; 129,5</t>
+          <t>19,29; 127,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>53,49; 175,14</t>
+          <t>42,06; 154,97</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>8,61</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,85</t>
+          <t>31,0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12,49</t>
+          <t>13,38</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,98; 70,59</t>
+          <t>18,98; 70,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 49,19</t>
+          <t>-16,63; 50,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 35,36</t>
+          <t>-18,95; 36,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 83,59</t>
+          <t>-3,15; 82,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,23; 100,0</t>
+          <t>10,79; 100,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 58,24</t>
+          <t>-13,62; 56,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,12; 64,76</t>
+          <t>20,48; 65,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 55,12</t>
+          <t>1,36; 56,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 32,32</t>
+          <t>-8,74; 34,09</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>215,26%</t>
+          <t>216,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>39,65%</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>30,11; 311,76</t>
+          <t>38,94; 330,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 183,58</t>
+          <t>-33,23; 204,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-39,76; 146,67</t>
+          <t>-35,65; 148,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,21; 350,24</t>
+          <t>44,37; 330,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 260,24</t>
+          <t>6,96; 283,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 158,33</t>
+          <t>-21,24; 177,62</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21,56</t>
+          <t>24,07</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,67</t>
+          <t>16,05</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19,01</t>
+          <t>20,52</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 37,74</t>
+          <t>-6,34; 37,57</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-31,25; 20,71</t>
+          <t>-28,74; 22,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 43,28</t>
+          <t>0,84; 44,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-50,27; 18,84</t>
+          <t>-47,16; 19,03</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,97; 73,01</t>
+          <t>9,14; 74,34</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 42,99</t>
+          <t>-11,8; 46,55</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 27,28</t>
+          <t>-9,61; 25,86</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 29,66</t>
+          <t>-16,18; 28,78</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,63; 36,25</t>
+          <t>2,93; 36,96</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>50,58%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 137,14</t>
+          <t>-11,8; 139,32</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-63,68; 64,99</t>
+          <t>-59,0; 79,05</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 155,39</t>
+          <t>2,79; 161,2</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-84,92; 108,5</t>
+          <t>-85,94; 98,13</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13,63; 386,15</t>
+          <t>16,82; 393,82</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 205,27</t>
+          <t>-19,17; 260,05</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 91,18</t>
+          <t>-20,56; 88,52</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-33,01; 93,71</t>
+          <t>-32,9; 92,28</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5,18; 121,28</t>
+          <t>5,76; 126,18</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7,54</t>
+          <t>9,25</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,13</t>
+          <t>13,07</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>11,23</t>
+          <t>11,54</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-25,13; 11,0</t>
+          <t>-26,2; 10,09</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 32,0</t>
+          <t>0,92; 33,97</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 23,41</t>
+          <t>-5,58; 25,72</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 25,34</t>
+          <t>-13,52; 29,43</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 28,27</t>
+          <t>-14,78; 25,91</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 31,05</t>
+          <t>-4,67; 30,44</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 11,99</t>
+          <t>-14,58; 12,38</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,04; 24,53</t>
+          <t>-0,02; 24,53</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 23,48</t>
+          <t>-1,39; 22,24</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-45,92; 27,7</t>
+          <t>-47,67; 24,13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,69; 80,61</t>
+          <t>0,39; 84,19</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 57,82</t>
+          <t>-10,06; 60,86</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-25,9; 63,15</t>
+          <t>-22,67; 75,28</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 72,57</t>
+          <t>-24,06; 65,05</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 83,14</t>
+          <t>-6,77; 79,11</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 26,67</t>
+          <t>-26,68; 29,01</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>1,86; 57,63</t>
+          <t>0,01; 56,75</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 56,21</t>
+          <t>-2,06; 52,37</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12,82</t>
+          <t>12,43</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-10,65</t>
+          <t>-15,89</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>-0,5</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-37,17; -3,83</t>
+          <t>-37,86; -4,21</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-44,81; -6,75</t>
+          <t>-43,4; -6,71</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 26,48</t>
+          <t>-1,91; 26,04</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 14,73</t>
+          <t>-33,56; 13,59</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-35,35; 15,79</t>
+          <t>-35,85; 13,88</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 10,71</t>
+          <t>-33,15; 3,22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-29,92; -2,34</t>
+          <t>-30,61; -0,47</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-34,63; -3,71</t>
+          <t>-34,35; -4,1</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 12,57</t>
+          <t>-11,91; 10,96</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-16,61%</t>
+          <t>-24,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>-0,79%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-56,53; -6,15</t>
+          <t>-56,87; -6,53</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-66,47; -10,87</t>
+          <t>-66,64; -12,02</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 48,44</t>
+          <t>-2,49; 47,74</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-42,21; 26,4</t>
+          <t>-46,65; 25,5</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-52,88; 28,24</t>
+          <t>-52,6; 25,08</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 21,15</t>
+          <t>-45,57; 5,33</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-44,8; -3,88</t>
+          <t>-46,33; -1,86</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-52,45; -6,42</t>
+          <t>-51,91; -7,2</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 21,6</t>
+          <t>-17,56; 19,23</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9,25</t>
+          <t>11,02</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,54</t>
+          <t>9,2</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>11,35</t>
+          <t>10,08</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 10,44</t>
+          <t>-4,44; 10,88</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,07; 14,69</t>
+          <t>0,59; 15,06</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,59; 16,34</t>
+          <t>3,99; 18,41</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 8,83</t>
+          <t>-9,82; 9,17</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,34; 24,1</t>
+          <t>5,95; 24,23</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,7; 25,75</t>
+          <t>0,39; 17,01</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 7,75</t>
+          <t>-4,35; 7,32</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>4,89; 16,14</t>
+          <t>4,77; 16,24</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5,54; 17,43</t>
+          <t>4,77; 15,4</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 21,19</t>
+          <t>-8,12; 21,85</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>0,2; 29,9</t>
+          <t>1,06; 30,57</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2,79; 33,37</t>
+          <t>7,19; 37,8</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 18,63</t>
+          <t>-17,65; 19,28</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>10,71; 51,4</t>
+          <t>10,39; 52,6</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>7,51; 52,87</t>
+          <t>0,69; 36,95</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 16,0</t>
+          <t>-7,96; 14,97</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>9,09; 32,63</t>
+          <t>9,31; 32,96</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>10,16; 35,26</t>
+          <t>8,84; 31,3</t>
         </is>
       </c>
     </row>
